--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260929.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260929.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>11.96%</t>
+          <t>11.64%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.74%</t>
+          <t>10.71%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.00%</t>
+          <t>8.01%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.17%</t>
+          <t>5.13%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.57%</t>
+          <t>4.94%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.11%</t>
+          <t>4.10%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.36%</t>
+          <t>3.30%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.27%</t>
+          <t>3.25%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.16%</t>
+          <t>3.08%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.48%</t>
+          <t>2.46%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.23%</t>
+          <t>2.24%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.49%</t>
         </is>
       </c>
     </row>
@@ -968,46 +968,46 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>1.31%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>FE US</t>
+          <t>PEG US</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>第一能源公司</t>
+          <t>大眾服務企業集團公司</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>76,601</t>
+          <t>49,536</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.17%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>PEG US</t>
+          <t>FE US</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>大眾服務企業集團公司</t>
+          <t>第一能源公司</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>49,536</t>
+          <t>76,601</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.11%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.11%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.08%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>1.05%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
@@ -1232,51 +1232,51 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.88%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>MTZ US</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>MasTec公司</t>
+          <t>PPL公司</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>11,237</t>
+          <t>74,774</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>ENS US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>PPL公司</t>
+          <t>EnerSys</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>74,774</t>
+          <t>13,152</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.83%</t>
         </is>
       </c>
     </row>
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>ENS US</t>
+          <t>MTZ US</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>EnerSys</t>
+          <t>MasTec公司</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>13,152</t>
+          <t>11,237</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>0.78%</t>
         </is>
       </c>
     </row>
@@ -1393,39 +1393,39 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>AGX US</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>阿根公司</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>145,345</t>
+          <t>4,921</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.65%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>AGX US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>阿根公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>4,921</t>
+          <t>145,345</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,61 +1437,61 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>LNT US</t>
+          <t>VICR US</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>聯合能源公司</t>
+          <t>懷克爾公司</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>25,581</t>
+          <t>5,778</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.58%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>LNT US</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>聯合能源公司</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>43,283</t>
+          <t>25,581</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.57%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>VICR US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>懷克爾公司</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>5,778</t>
+          <t>43,283</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.52%</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.44%</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.37%</t>
         </is>
       </c>
     </row>
@@ -1628,51 +1628,51 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.26%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>BELFB US</t>
+          <t>ITRI US</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>百富電子有限公司</t>
+          <t>英特隆公司</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>2,839</t>
+          <t>7,921</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.24%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>ITRI US</t>
+          <t>BELFB US</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>英特隆公司</t>
+          <t>百富電子有限公司</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>7,921</t>
+          <t>2,839</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.24%</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1729,7 @@
       <c r="B72" s="3" t="inlineStr"/>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>152,756,508</t>
+          <t>166,489,369</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr"/>
